--- a/進捗/PlayerAnimaiton.xlsx
+++ b/進捗/PlayerAnimaiton.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_winter\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4AAB2E-7129-411E-9E5E-54F2A8372C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51AEFDE-311C-4B22-94E6-721EF18A81E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6750" yWindow="4485" windowWidth="20625" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5775" yWindow="3075" windowWidth="27105" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -409,4 +410,14 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8759246E-022F-41CC-8FDB-28555489C47E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>